--- a/menu.xlsx
+++ b/menu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a80709efb6200ae/Desktop/גיבוי/בית ספר/חומרים אינטרקטיבים/לומדות מוכנות/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{33A27E57-3E44-4A49-85D6-ADCCA7BA1D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{33A27E57-3E44-4A49-85D6-ADCCA7BA1D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CE3936D-6C14-404F-A67D-C3B989E8F55A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{498D3550-708E-438F-8EC4-B38F0D88E414}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>page_name</t>
   </si>
@@ -73,6 +73,12 @@
   </si>
   <si>
     <t>מערכת הנשימה</t>
+  </si>
+  <si>
+    <t>מערכת הרבייה</t>
+  </si>
+  <si>
+    <t>https://tanyatabakmaher.github.io/haklaut/maarehet-revaya.html</t>
   </si>
 </sst>
 </file>
@@ -425,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B026AC43-3F7F-45AF-806E-B0659676E60E}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.9140625" customWidth="1"/>
@@ -480,6 +486,14 @@
         <v>10</v>
       </c>
     </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/menu.xlsx
+++ b/menu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a80709efb6200ae/Desktop/גיבוי/בית ספר/חומרים אינטרקטיבים/לומדות מוכנות/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{33A27E57-3E44-4A49-85D6-ADCCA7BA1D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CE3936D-6C14-404F-A67D-C3B989E8F55A}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="8_{33A27E57-3E44-4A49-85D6-ADCCA7BA1D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1357C546-95A0-47B6-9956-D69EB900F440}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{498D3550-708E-438F-8EC4-B38F0D88E414}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>page_name</t>
   </si>
@@ -79,16 +79,46 @@
   </si>
   <si>
     <t>https://tanyatabakmaher.github.io/haklaut/maarehet-revaya.html</t>
+  </si>
+  <si>
+    <t>menu_icon</t>
+  </si>
+  <si>
+    <t>https://tanyatabakmaher.github.io/haklaut/bg/mavo.png</t>
+  </si>
+  <si>
+    <t>https://tanyatabakmaher.github.io/haklaut/bg/visut.png</t>
+  </si>
+  <si>
+    <t>https://tanyatabakmaher.github.io/haklaut/bg/visut-haklai.png</t>
+  </si>
+  <si>
+    <t>https://tanyatabakmaher.github.io/haklaut/bg/hisun.png</t>
+  </si>
+  <si>
+    <t>https://tanyatabakmaher.github.io/haklaut/bg/neshima.png</t>
+  </si>
+  <si>
+    <t>https://tanyatabakmaher.github.io/haklaut/bg/revaya.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="177"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="177"/>
@@ -112,13 +142,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -431,70 +464,101 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B026AC43-3F7F-45AF-806E-B0659676E60E}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.9140625" customWidth="1"/>
-    <col min="2" max="2" width="19.58203125" customWidth="1"/>
+    <col min="2" max="2" width="25.83203125" customWidth="1"/>
+    <col min="3" max="3" width="29.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C3" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C4" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C5" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C6" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
       </c>
+      <c r="C7" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{3F08E3EC-5CAE-4D20-8ED6-CA53A0399477}"/>
+    <hyperlink ref="C2" r:id="rId2" xr:uid="{5B7C2E5E-FF93-4D57-9D21-5E1CE71A6E26}"/>
+    <hyperlink ref="C3" r:id="rId3" xr:uid="{9F886686-24BD-404C-8510-11CE4016BC5E}"/>
+    <hyperlink ref="C4" r:id="rId4" xr:uid="{A5633CDD-BA5F-4464-9AF3-41D9D333F7A0}"/>
+    <hyperlink ref="C5" r:id="rId5" xr:uid="{0420DAF3-5C87-4EF0-86B0-C9EC73041236}"/>
+    <hyperlink ref="C6" r:id="rId6" xr:uid="{1E8E77D7-0763-44D9-A2C1-CE019D205ABE}"/>
+    <hyperlink ref="C7" r:id="rId7" xr:uid="{65A3D81C-4BDC-47AA-B7B8-A5836CDE36EF}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/menu.xlsx
+++ b/menu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a80709efb6200ae/Desktop/גיבוי/בית ספר/חומרים אינטרקטיבים/לומדות מוכנות/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="8_{33A27E57-3E44-4A49-85D6-ADCCA7BA1D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1357C546-95A0-47B6-9956-D69EB900F440}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="8_{33A27E57-3E44-4A49-85D6-ADCCA7BA1D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55ADF02E-4EDC-4317-A21A-801E5DA53FB4}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{498D3550-708E-438F-8EC4-B38F0D88E414}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
   <si>
     <t>page_name</t>
   </si>
@@ -100,6 +100,24 @@
   </si>
   <si>
     <t>https://tanyatabakmaher.github.io/haklaut/bg/revaya.png</t>
+  </si>
+  <si>
+    <t>general</t>
+  </si>
+  <si>
+    <t>dogs</t>
+  </si>
+  <si>
+    <t>https://tanyatabakmaher.github.io/haklaut/klavim/tkufot-kritiyot.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">תקופות קריטיות </t>
+  </si>
+  <si>
+    <t>https://tanyatabakmaher.github.io/haklaut/bg/klavin/tkufot.png</t>
+  </si>
+  <si>
+    <t>topic</t>
   </si>
 </sst>
 </file>
@@ -464,15 +482,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B026AC43-3F7F-45AF-806E-B0659676E60E}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.9140625" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
     <col min="3" max="3" width="29.6640625" customWidth="1"/>
+    <col min="4" max="4" width="18.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -482,8 +501,11 @@
       <c r="C1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -493,8 +515,11 @@
       <c r="C2" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -504,8 +529,11 @@
       <c r="C3" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -515,8 +543,11 @@
       <c r="C4" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -526,8 +557,11 @@
       <c r="C5" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -537,8 +571,11 @@
       <c r="C6" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -547,6 +584,23 @@
       </c>
       <c r="C7" s="1" t="s">
         <v>20</v>
+      </c>
+      <c r="D7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -558,6 +612,7 @@
     <hyperlink ref="C5" r:id="rId5" xr:uid="{0420DAF3-5C87-4EF0-86B0-C9EC73041236}"/>
     <hyperlink ref="C6" r:id="rId6" xr:uid="{1E8E77D7-0763-44D9-A2C1-CE019D205ABE}"/>
     <hyperlink ref="C7" r:id="rId7" xr:uid="{65A3D81C-4BDC-47AA-B7B8-A5836CDE36EF}"/>
+    <hyperlink ref="C8" r:id="rId8" xr:uid="{B9CC987C-C4B1-4390-B0CD-E686D05DFA3D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/menu.xlsx
+++ b/menu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a80709efb6200ae/Desktop/גיבוי/בית ספר/חומרים אינטרקטיבים/לומדות מוכנות/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="8_{33A27E57-3E44-4A49-85D6-ADCCA7BA1D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55ADF02E-4EDC-4317-A21A-801E5DA53FB4}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="8_{33A27E57-3E44-4A49-85D6-ADCCA7BA1D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53466CD6-71D7-4765-BE04-BDCCA5F24F34}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{498D3550-708E-438F-8EC4-B38F0D88E414}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
   <si>
     <t>page_name</t>
   </si>
@@ -118,6 +118,15 @@
   </si>
   <si>
     <t>topic</t>
+  </si>
+  <si>
+    <t>https://tanyatabakmaher.github.io/haklaut/bg/ikul.png</t>
+  </si>
+  <si>
+    <t>https://tanyatabakmaher.github.io/haklaut/ikul.html</t>
+  </si>
+  <si>
+    <t>מערכת העיכול</t>
   </si>
 </sst>
 </file>
@@ -482,7 +491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B026AC43-3F7F-45AF-806E-B0659676E60E}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.9140625" customWidth="1"/>
@@ -565,7 +574,7 @@
       <c r="A6" t="s">
         <v>11</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -577,13 +586,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
+        <v>29</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
         <v>21</v>
@@ -591,15 +600,29 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>24</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B9" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D9" t="s">
         <v>22</v>
       </c>
     </row>
@@ -611,8 +634,11 @@
     <hyperlink ref="C4" r:id="rId4" xr:uid="{A5633CDD-BA5F-4464-9AF3-41D9D333F7A0}"/>
     <hyperlink ref="C5" r:id="rId5" xr:uid="{0420DAF3-5C87-4EF0-86B0-C9EC73041236}"/>
     <hyperlink ref="C6" r:id="rId6" xr:uid="{1E8E77D7-0763-44D9-A2C1-CE019D205ABE}"/>
-    <hyperlink ref="C7" r:id="rId7" xr:uid="{65A3D81C-4BDC-47AA-B7B8-A5836CDE36EF}"/>
-    <hyperlink ref="C8" r:id="rId8" xr:uid="{B9CC987C-C4B1-4390-B0CD-E686D05DFA3D}"/>
+    <hyperlink ref="C8" r:id="rId7" xr:uid="{65A3D81C-4BDC-47AA-B7B8-A5836CDE36EF}"/>
+    <hyperlink ref="C9" r:id="rId8" xr:uid="{B9CC987C-C4B1-4390-B0CD-E686D05DFA3D}"/>
+    <hyperlink ref="C7" r:id="rId9" xr:uid="{2402C49A-7D42-44AD-9335-3BB0432A3A1A}"/>
+    <hyperlink ref="B6" r:id="rId10" xr:uid="{7517147F-D231-45F6-8908-95B66EE43EAC}"/>
+    <hyperlink ref="B7" r:id="rId11" xr:uid="{119C3298-48AF-47F3-B5F4-812F2FBD31A4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/menu.xlsx
+++ b/menu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a80709efb6200ae/Desktop/גיבוי/בית ספר/חומרים אינטרקטיבים/לומדות מוכנות/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="45" documentId="8_{33A27E57-3E44-4A49-85D6-ADCCA7BA1D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53466CD6-71D7-4765-BE04-BDCCA5F24F34}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="8_{33A27E57-3E44-4A49-85D6-ADCCA7BA1D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D21718A-311D-471B-A873-C22474B032E0}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{498D3550-708E-438F-8EC4-B38F0D88E414}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
   <si>
     <t>page_name</t>
   </si>
@@ -127,6 +127,15 @@
   </si>
   <si>
     <t>מערכת העיכול</t>
+  </si>
+  <si>
+    <t>רבייה</t>
+  </si>
+  <si>
+    <t>https://tanyatabakmaher.github.io/haklaut/klavim/reviya.html</t>
+  </si>
+  <si>
+    <t>https://tanyatabakmaher.github.io/haklaut/bg/klavin/dog-reviya.png</t>
   </si>
 </sst>
 </file>
@@ -491,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B026AC43-3F7F-45AF-806E-B0659676E60E}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.9140625" customWidth="1"/>
@@ -616,13 +625,27 @@
       <c r="A9" t="s">
         <v>24</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s">
         <v>22</v>
       </c>
     </row>
@@ -639,6 +662,9 @@
     <hyperlink ref="C7" r:id="rId9" xr:uid="{2402C49A-7D42-44AD-9335-3BB0432A3A1A}"/>
     <hyperlink ref="B6" r:id="rId10" xr:uid="{7517147F-D231-45F6-8908-95B66EE43EAC}"/>
     <hyperlink ref="B7" r:id="rId11" xr:uid="{119C3298-48AF-47F3-B5F4-812F2FBD31A4}"/>
+    <hyperlink ref="B9" r:id="rId12" xr:uid="{513D8D30-3F75-490B-B291-D14B90226E33}"/>
+    <hyperlink ref="B10" r:id="rId13" xr:uid="{85602228-8211-454E-9E45-26DB0D927C0F}"/>
+    <hyperlink ref="C10" r:id="rId14" xr:uid="{BF36189E-474B-48FC-986F-A4627A52C309}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/menu.xlsx
+++ b/menu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a80709efb6200ae/Desktop/גיבוי/בית ספר/חומרים אינטרקטיבים/לומדות מוכנות/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="53" documentId="8_{33A27E57-3E44-4A49-85D6-ADCCA7BA1D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D21718A-311D-471B-A873-C22474B032E0}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="8_{33A27E57-3E44-4A49-85D6-ADCCA7BA1D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E7F7BF1-3050-47A5-AC2C-33872397631E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{498D3550-708E-438F-8EC4-B38F0D88E414}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
   <si>
     <t>page_name</t>
   </si>
@@ -136,6 +136,15 @@
   </si>
   <si>
     <t>https://tanyatabakmaher.github.io/haklaut/bg/klavin/dog-reviya.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הזנה וטיפוח </t>
+  </si>
+  <si>
+    <t>https://tanyatabakmaher.github.io/haklaut/klavim/hazana-parva.html</t>
+  </si>
+  <si>
+    <t>https://tanyatabakmaher.github.io/haklaut/bg/klavin/mazon.png</t>
   </si>
 </sst>
 </file>
@@ -500,7 +509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B026AC43-3F7F-45AF-806E-B0659676E60E}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.9140625" customWidth="1"/>
@@ -646,6 +655,20 @@
         <v>32</v>
       </c>
       <c r="D10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" t="s">
         <v>22</v>
       </c>
     </row>
@@ -665,6 +688,8 @@
     <hyperlink ref="B9" r:id="rId12" xr:uid="{513D8D30-3F75-490B-B291-D14B90226E33}"/>
     <hyperlink ref="B10" r:id="rId13" xr:uid="{85602228-8211-454E-9E45-26DB0D927C0F}"/>
     <hyperlink ref="C10" r:id="rId14" xr:uid="{BF36189E-474B-48FC-986F-A4627A52C309}"/>
+    <hyperlink ref="C11" r:id="rId15" xr:uid="{18DB512F-3622-485E-AB55-7A1A43B47F6B}"/>
+    <hyperlink ref="B11" r:id="rId16" xr:uid="{7F9343F3-483B-47E3-BCE6-087AB06A5E42}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/menu.xlsx
+++ b/menu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a80709efb6200ae/Desktop/גיבוי/בית ספר/חומרים אינטרקטיבים/לומדות מוכנות/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="8_{33A27E57-3E44-4A49-85D6-ADCCA7BA1D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E7F7BF1-3050-47A5-AC2C-33872397631E}"/>
+  <xr:revisionPtr revIDLastSave="65" documentId="8_{33A27E57-3E44-4A49-85D6-ADCCA7BA1D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF7BB935-AB76-4649-8A03-05B40B77834F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{498D3550-708E-438F-8EC4-B38F0D88E414}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
   <si>
     <t>page_name</t>
   </si>
@@ -145,6 +145,15 @@
   </si>
   <si>
     <t>https://tanyatabakmaher.github.io/haklaut/bg/klavin/mazon.png</t>
+  </si>
+  <si>
+    <t>כלבת</t>
+  </si>
+  <si>
+    <t>https://tanyatabakmaher.github.io/haklaut/bg/klavin/kalevet.png</t>
+  </si>
+  <si>
+    <t>https://tanyatabakmaher.github.io/haklaut/klavim/kalevet.html</t>
   </si>
 </sst>
 </file>
@@ -509,7 +518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B026AC43-3F7F-45AF-806E-B0659676E60E}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.9140625" customWidth="1"/>
@@ -669,6 +678,20 @@
         <v>35</v>
       </c>
       <c r="D11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" t="s">
         <v>22</v>
       </c>
     </row>
@@ -690,6 +713,8 @@
     <hyperlink ref="C10" r:id="rId14" xr:uid="{BF36189E-474B-48FC-986F-A4627A52C309}"/>
     <hyperlink ref="C11" r:id="rId15" xr:uid="{18DB512F-3622-485E-AB55-7A1A43B47F6B}"/>
     <hyperlink ref="B11" r:id="rId16" xr:uid="{7F9343F3-483B-47E3-BCE6-087AB06A5E42}"/>
+    <hyperlink ref="C12" r:id="rId17" xr:uid="{EEA251E9-BB9D-4ED2-8884-85CF4894F9B4}"/>
+    <hyperlink ref="B12" r:id="rId18" xr:uid="{D54F77F3-7EBA-4EDB-BA20-9F72E40554AC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/menu.xlsx
+++ b/menu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a80709efb6200ae/Desktop/גיבוי/בית ספר/חומרים אינטרקטיבים/לומדות מוכנות/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="8_{33A27E57-3E44-4A49-85D6-ADCCA7BA1D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF7BB935-AB76-4649-8A03-05B40B77834F}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="8_{33A27E57-3E44-4A49-85D6-ADCCA7BA1D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D16D1AE7-E3D1-440C-ABC6-38EC27F91F20}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{498D3550-708E-438F-8EC4-B38F0D88E414}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="51">
   <si>
     <t>page_name</t>
   </si>
@@ -154,6 +154,42 @@
   </si>
   <si>
     <t>https://tanyatabakmaher.github.io/haklaut/klavim/kalevet.html</t>
+  </si>
+  <si>
+    <t>sub_title</t>
+  </si>
+  <si>
+    <t>מהי חקלאות, תיאוריית מלתוס, המהפכה הירוקה, שיפורים טכנולוגיים והקשר בין ייצור מזון, כלכלה וסביבה.</t>
+  </si>
+  <si>
+    <t>הומאותרמיים ופויקילותרמיים, מנגנוני ויסות חום, מעבר חום, חילוף חומרים ועומס חום בסביבה.</t>
+  </si>
+  <si>
+    <t>תנאי ממשק, ויסות חום בעוף, תכנון הלול, אוורור, קירור, חימום ומבנים מבוקרי אקלים.</t>
+  </si>
+  <si>
+    <t>תפקידי מערכת הנשימה, חילוף גזים ודיפוזיה, מבנה הנשימה ביונקים, עופות, דבורים וכלבים.</t>
+  </si>
+  <si>
+    <t>מבנה מערכת הרבייה, ביוץ והפריה, מחזורי רבייה, הורמונים והתערבות האדם ברבייה חקלאית.</t>
+  </si>
+  <si>
+    <t>מחלות ודרכי הדבקה, קווי ההגנה של הגוף, מערכת החיסון וההבדל בין חיסון פעיל לחיסון סביל.</t>
+  </si>
+  <si>
+    <t>מבנה מערכת העיכול, פירוק מכני וכימי של המזון, מים ומינרלים, ואבות המזון שהגוף צריך לתפקוד תקין.</t>
+  </si>
+  <si>
+    <t>מושגי יסוד בהתפתחות הגור, שבע התקופות הקריטיות, חשיפה והחתמה נכונה, ובחירת גור מתאים.</t>
+  </si>
+  <si>
+    <t>מחזור הרבייה בכלבות, שלבי הייחום, היריון, המלטה, טיפול בגורים, מניעת היריון ועיקור.</t>
+  </si>
+  <si>
+    <t>מטרות ההזנה, מערכת העיכול, מזונות אסורים, חישוב קלוריות, סוגי מזון ומבנה העור והפרווה בכלב.</t>
+  </si>
+  <si>
+    <t>פקודת הכלבת, מחלה זואונוטית, דרכי הדבקה, סימני המחלה, מניעה, וחיסון פעיל מול חיסון סביל.</t>
   </si>
 </sst>
 </file>
@@ -518,7 +554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B026AC43-3F7F-45AF-806E-B0659676E60E}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.9140625" customWidth="1"/>
@@ -527,7 +563,7 @@
     <col min="4" max="4" width="18.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -540,8 +576,11 @@
       <c r="D1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -554,8 +593,11 @@
       <c r="D2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -568,8 +610,11 @@
       <c r="D3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -582,8 +627,11 @@
       <c r="D4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -596,8 +644,11 @@
       <c r="D5" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -610,8 +661,11 @@
       <c r="D6" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -624,8 +678,11 @@
       <c r="D7" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -638,8 +695,11 @@
       <c r="D8" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -652,8 +712,11 @@
       <c r="D9" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -666,8 +729,11 @@
       <c r="D10" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -680,8 +746,11 @@
       <c r="D11" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -693,6 +762,9 @@
       </c>
       <c r="D12" t="s">
         <v>22</v>
+      </c>
+      <c r="E12" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/menu.xlsx
+++ b/menu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a80709efb6200ae/Desktop/גיבוי/בית ספר/חומרים אינטרקטיבים/לומדות מוכנות/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="8_{33A27E57-3E44-4A49-85D6-ADCCA7BA1D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D16D1AE7-E3D1-440C-ABC6-38EC27F91F20}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="8_{33A27E57-3E44-4A49-85D6-ADCCA7BA1D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67CF328B-E39F-45BA-B2A0-E16E3450F265}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{498D3550-708E-438F-8EC4-B38F0D88E414}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="55">
   <si>
     <t>page_name</t>
   </si>
@@ -190,6 +190,18 @@
   </si>
   <si>
     <t>פקודת הכלבת, מחלה זואונוטית, דרכי הדבקה, סימני המחלה, מניעה, וחיסון פעיל מול חיסון סביל.</t>
+  </si>
+  <si>
+    <t>יצרים</t>
+  </si>
+  <si>
+    <t>https://tanyatabakmaher.github.io/haklaut/klavim/yezarim.html</t>
+  </si>
+  <si>
+    <t>https://tanyatabakmaher.github.io/haklaut/bg/klavin/yezarim.png</t>
+  </si>
+  <si>
+    <t>מה מניע את הכלב: יצרים, דחפים, תכונות, מזג ותחומי הדיגר</t>
   </si>
 </sst>
 </file>
@@ -554,7 +566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B026AC43-3F7F-45AF-806E-B0659676E60E}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.9140625" customWidth="1"/>
@@ -765,6 +777,23 @@
       </c>
       <c r="E12" t="s">
         <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -787,6 +816,8 @@
     <hyperlink ref="B11" r:id="rId16" xr:uid="{7F9343F3-483B-47E3-BCE6-087AB06A5E42}"/>
     <hyperlink ref="C12" r:id="rId17" xr:uid="{EEA251E9-BB9D-4ED2-8884-85CF4894F9B4}"/>
     <hyperlink ref="B12" r:id="rId18" xr:uid="{D54F77F3-7EBA-4EDB-BA20-9F72E40554AC}"/>
+    <hyperlink ref="C13" r:id="rId19" xr:uid="{D40292C3-27B3-4AA1-8410-555541F03DD4}"/>
+    <hyperlink ref="B13" r:id="rId20" xr:uid="{B50778ED-3CC4-43A6-8CC9-F9610CED6D3A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/menu.xlsx
+++ b/menu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a80709efb6200ae/Desktop/גיבוי/בית ספר/חומרים אינטרקטיבים/לומדות מוכנות/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="8_{33A27E57-3E44-4A49-85D6-ADCCA7BA1D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{67CF328B-E39F-45BA-B2A0-E16E3450F265}"/>
+  <xr:revisionPtr revIDLastSave="91" documentId="8_{33A27E57-3E44-4A49-85D6-ADCCA7BA1D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC8CA3EB-4422-4430-803D-47A74A208D45}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{498D3550-708E-438F-8EC4-B38F0D88E414}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="59">
   <si>
     <t>page_name</t>
   </si>
@@ -202,6 +202,18 @@
   </si>
   <si>
     <t>מה מניע את הכלב: יצרים, דחפים, תכונות, מזג ותחומי הדיגר</t>
+  </si>
+  <si>
+    <t>כיצד כלבים לומדים</t>
+  </si>
+  <si>
+    <t>https://tanyatabakmaher.github.io/haklaut/klavim/lemida.html</t>
+  </si>
+  <si>
+    <t>https://tanyatabakmaher.github.io/haklaut/bg/klavin/lemida.png</t>
+  </si>
+  <si>
+    <t>תקופות קריטיות, אינסטינקט, רפלקס, התניה קלאסית ואופרנטית, חיזוקים ועונש</t>
   </si>
 </sst>
 </file>
@@ -566,7 +578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B026AC43-3F7F-45AF-806E-B0659676E60E}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.9140625" customWidth="1"/>
@@ -794,6 +806,23 @@
       </c>
       <c r="E13" t="s">
         <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -818,6 +847,8 @@
     <hyperlink ref="B12" r:id="rId18" xr:uid="{D54F77F3-7EBA-4EDB-BA20-9F72E40554AC}"/>
     <hyperlink ref="C13" r:id="rId19" xr:uid="{D40292C3-27B3-4AA1-8410-555541F03DD4}"/>
     <hyperlink ref="B13" r:id="rId20" xr:uid="{B50778ED-3CC4-43A6-8CC9-F9610CED6D3A}"/>
+    <hyperlink ref="C14" r:id="rId21" xr:uid="{911EC805-60C2-4E6A-8C4A-33407EAE8CF4}"/>
+    <hyperlink ref="B14" r:id="rId22" xr:uid="{EBC0AA92-E021-497F-B4EA-CF4C1550338B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
